--- a/branches/feat/search-parameters-page/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/branches/feat/search-parameters-page/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-05T12:03:43+00:00</t>
+    <t>2026-09-05T12:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
